--- a/excel/Ch11_Accruals_Prepayments.xlsx
+++ b/excel/Ch11_Accruals_Prepayments.xlsx
@@ -229,7 +229,7 @@
     <t xml:space="preserve">Use the data below.</t>
   </si>
   <si>
-    <t xml:space="preserve">Model Question 11.8 (Zara, year ended 31 March 2026)</t>
+    <t xml:space="preserve">Model Question 11.11 (Zara, year ended 31 March 2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Wages owing at 1 April 2025</t>
@@ -274,7 +274,7 @@
     <t xml:space="preserve">Check</t>
   </si>
   <si>
-    <t xml:space="preserve">Model Question 11.8</t>
+    <t xml:space="preserve">Model Question 11.11</t>
   </si>
   <si>
     <t xml:space="preserve">Wages expense for the SPL</t>
